--- a/dataset/stats/Ground/Japan_Realistic.xlsx
+++ b/dataset/stats/Ground/Japan_Realistic.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,76 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Rank_Info</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Сыграно игр</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Победы</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Процент побед</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Возрождения</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Наземные убийства</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Воздушные убийства</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Морские убийства</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Смерти</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Убийств за возрождение</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Убийств за смерть</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SL за игру</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RP за игру</t>
         </is>
@@ -491,70 +508,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>jp_type_90b_camo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Type90(B)""Fuji</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.7#1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>1,202,769</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>595,974</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>49.6%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1,552,455</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>1,924,921</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>12,651</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>1,440,290</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>18,785</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1,524</t>
         </is>
@@ -563,70 +585,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>jp_type_10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Type10</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>553,970</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>292,178</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>52.7%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>616,769</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>833,750</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>5,142</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>558,113</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>8,046</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>757</t>
         </is>
@@ -635,70 +662,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>jp_tkx_prot</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>TKX</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>474,199</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>253,617</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>53.5%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>520,490</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>743,127</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>4,417</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>466,313</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>8,504</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>819</t>
         </is>
@@ -707,70 +739,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>jp_type_90</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Type90</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.7#4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>403,679</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>197,445</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>48.9%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>457,876</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>482,374</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>3,898</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>405,051</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>6,535</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>606</t>
         </is>
@@ -779,70 +816,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>jp_type_16_mod</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Type16(FPS)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>311,563</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>160,334</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>51.5%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>384,988</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>369,501</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>3,454</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>352,833</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>13,463</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>1,188</t>
         </is>
@@ -851,70 +893,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>jp_type_87</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Type87</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.3#6</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>304,015</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>136,933</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>45.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>371,665</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>186,545</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>73,954</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>300,082</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4,458</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>330</t>
         </is>
@@ -923,70 +970,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>jp_oplot_t</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>BMOplot-T</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.3#7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>283,849</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>151,327</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>53.3%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>337,210</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>399,026</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2,238</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>304,174</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>7,796</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>699</t>
         </is>
@@ -995,70 +1047,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>jp_m24_chaffee</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>▅M24</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.7#8</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>273,344</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>152,733</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>55.9%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>308,069</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>330,846</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>11,107</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>268,882</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2,797</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>305</t>
         </is>
@@ -1067,70 +1124,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>jp_type_90b</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Type90(B)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.7#9</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>265,857</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>131,524</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>49.5%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>295,414</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>312,758</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2,484</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>259,344</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>6,666</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>618</t>
         </is>
@@ -1139,70 +1201,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>jp_type_89</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Type89</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#10</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>252,112</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>129,183</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>51.2%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>279,927</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>251,989</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>6,882</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>242,951</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>5,057</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>445</t>
         </is>
@@ -1211,70 +1278,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>jp_type_16_mcv_prot</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Type16(P)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#11</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>249,684</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>127,342</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>51.0%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>278,880</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>234,755</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2,343</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>252,065</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>4,688</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>408</t>
         </is>
@@ -1283,70 +1355,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>jp_type_10_prototype</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>TKX(P)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Ранг 7БР 12.0#12</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>247,762</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>128,157</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>51.7%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>283,374</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>321,273</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2,327</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>246,715</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>7,153</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>691</t>
         </is>
@@ -1355,70 +1432,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>jp_sub_i_ii_20mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>SUB-I-II</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.3#13</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>243,841</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>116,445</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>47.8%</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>278,975</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>88,629</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>75,316</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>212,722</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>3,477</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>257</t>
         </is>
@@ -1427,70 +1509,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>jp_type_74</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Type74(E)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#14</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>225,427</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>114,253</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>50.7%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>249,171</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>265,656</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2,366</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>216,522</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>6,224</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>459</t>
         </is>
@@ -1499,70 +1586,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>jp_type_5_ho_ri_production</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Ho-RiProduction</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.3#15</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>214,402</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>122,095</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>56.9%</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>247,467</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>495,031</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>706</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>206,483</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>11,089</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>667</t>
         </is>
@@ -1571,70 +1663,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>jp_st_b1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>STB-2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.3#16</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>201,598</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>105,531</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>230,682</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>210,503</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>2,913</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>204,863</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>5,878</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>399</t>
         </is>
@@ -1643,70 +1740,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>jp_type_61</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Type61</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>194,839</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>99,208</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>50.9%</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>216,391</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>175,686</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2,905</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>191,280</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>4,885</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>314</t>
         </is>
@@ -1715,70 +1817,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>jp_type_60_sprg</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Type60SPRG(C)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#18</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>186,385</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>94,998</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>51.0%</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>205,584</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>173,335</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>178,621</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>5,355</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>320</t>
         </is>
@@ -1787,70 +1894,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>jp_type_99</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Type99</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.3#19</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>184,252</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>92,339</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>50.1%</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>202,480</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>142,550</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>26,587</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>164,479</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>4,775</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>293</t>
         </is>
@@ -1859,70 +1971,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>jp_m41_walker_bulldog</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>▅M41A1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#20</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>184,221</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>94,666</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>51.4%</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>200,197</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>142,329</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>4,339</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>176,408</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>4,027</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>306</t>
         </is>
@@ -1931,70 +2048,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>jp_m36b2_jgsdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>▅M36</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.7#21</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>182,778</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>93,547</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>51.2%</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>207,871</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>181,736</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>4,687</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>184,663</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>4,567</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>293</t>
         </is>
@@ -2003,70 +2125,75 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>jp_m4a3e8_76w_sherman</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>▅M4A3(76)W</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.7#22</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>161,633</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>85,873</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>53.1%</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>179,568</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>195,005</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>5,121</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>156,905</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>1.28</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>4,947</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>341</t>
         </is>
@@ -2075,70 +2202,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>jp_type_74_c</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Type74(C)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.3#23</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>153,366</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>81,883</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>53.4%</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>174,012</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>174,833</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>2,362</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>152,975</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>6,497</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>444</t>
         </is>
@@ -2147,70 +2279,75 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>jp_st_a1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>ST-A1</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#24</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>151,628</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>75,602</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>49.9%</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>168,197</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>149,885</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>3,475</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>146,340</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>4,655</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>308</t>
         </is>
@@ -2219,70 +2356,75 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>jp_m60a3_tts</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>▄M60A3TTS</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#25</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>151,353</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>77,258</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>51.0%</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>171,690</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>175,354</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1,550</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>149,294</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>6,340</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>467</t>
         </is>
@@ -2291,70 +2433,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>jp_m47_patton_II</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>▅M47</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.3#26</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>148,209</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>77,734</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>52.4%</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>162,636</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>147,915</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>2,930</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>137,632</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>5,924</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>384</t>
         </is>
@@ -2363,70 +2510,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>jp_type_5_chi_ri</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Chi-Ri</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.7#27</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>148,071</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>77,468</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>164,561</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>185,226</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>362</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>144,069</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>4,540</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>319</t>
         </is>
@@ -2435,70 +2587,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>jp_type_87_rcv</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Type87RCV</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#28</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>147,937</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>79,243</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>53.6%</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>163,796</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>131,379</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>5,248</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>142,335</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>4,954</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>428</t>
         </is>
@@ -2507,70 +2664,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>jp_type_87_rcv_prot</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Type87RCV(P)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#29</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>145,213</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>78,021</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>53.7%</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>160,977</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>81,593</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>8,828</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>143,698</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>4,607</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>374</t>
         </is>
@@ -2579,70 +2741,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>jp_type_4_chi_to</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Chi-To</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.7#30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>144,416</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>79,601</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>55.1%</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>159,341</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>208,130</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>1,313</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>135,676</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>4,074</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>312</t>
         </is>
@@ -2651,70 +2818,75 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>jp_type_3_chi_nu_75cm_type_5</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Chi-NuII</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.3#31</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>137,052</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>79,487</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>58.0%</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>168,602</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>319,364</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>1,826</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>146,901</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>2.19</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>12,973</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>964</t>
         </is>
@@ -2723,70 +2895,75 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>jp_type_75</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Type75SPH</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#32</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>135,840</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>66,587</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>49.0%</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>149,275</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>106,451</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>12,136</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>123,589</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>4,482</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>272</t>
         </is>
@@ -2795,70 +2972,75 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>jp_type_74_mod_g_kai</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Type74(G)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#33</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>135,748</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>69,818</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>51.4%</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>163,486</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>198,947</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>1,378</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>144,675</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>16,469</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>1,175</t>
         </is>
@@ -2867,70 +3049,75 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>jp_navy_120mm_spg</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Chi-HaLG</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.0#34</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>132,181</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>68,158</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>51.6%</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>145,224</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>161,385</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>498</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>120,072</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>1,695</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>209</t>
         </is>
@@ -2939,70 +3126,75 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>jp_stingray</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>▄Stingray</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#35</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>131,684</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>68,960</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>52.4%</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>148,436</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>157,174</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>1,276</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>132,059</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>5,817</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>511</t>
         </is>
@@ -3011,70 +3203,75 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>jp_m42_duster</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>▅M42</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#36</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>129,937</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>66,239</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>51.0%</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>147,111</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>71,746</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>32,090</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>117,227</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>0.71</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>2,557</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>219</t>
         </is>
@@ -3083,70 +3280,75 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>jp_type_16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Type16</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.7#37</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>127,397</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>64,901</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>50.9%</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>141,501</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>118,295</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>1,270</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>124,528</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>5,049</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>501</t>
         </is>
@@ -3155,70 +3357,75 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>jp_type_3_chi_nu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Chi-Nu</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.3#38</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>123,755</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>64,572</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>52.2%</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>136,291</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>130,349</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>1,509</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>114,386</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>2,479</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>239</t>
         </is>
@@ -3227,70 +3434,75 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>jp_st_a3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>ST-A3</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#39</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>122,977</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>65,011</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>52.9%</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>136,662</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>152,548</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>3,212</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>119,044</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>6,400</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>412</t>
         </is>
@@ -3299,70 +3511,75 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>jp_icv_ifv_prototype</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Type24ICV(P)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.7#40</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>122,872</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>64,344</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>52.4%</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>138,107</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>106,868</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>8,464</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>120,710</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>5,409</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>495</t>
         </is>
@@ -3371,70 +3588,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>jp_type_93</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Type93</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.3#41</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>120,381</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>57,005</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>47.4%</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>144,600</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>75,601</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>90,367</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>3,753</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>279</t>
         </is>
@@ -3443,70 +3665,75 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>jp_m44</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>▅M44</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#42</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>115,505</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>59,577</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>51.6%</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>125,578</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>100,293</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>4,075</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>106,866</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>2,735</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>219</t>
         </is>
@@ -3515,70 +3742,75 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>jp_m163_vulcan</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>▄M163</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.3#43</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>113,073</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>52,928</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>46.8%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>128,216</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>25,816</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>48,597</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>92,254</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>3,604</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>227</t>
         </is>
@@ -3587,70 +3819,75 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>jp_type_4_chi_to_late</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Chi-ToLate</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.7#44</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>109,331</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>62,332</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>57.0%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>120,441</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>187,609</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1,054</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>101,387</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>1.57</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>5,223</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>375</t>
         </is>
@@ -3659,70 +3896,75 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>jp_type_74_f</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Type74(F)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#45</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>105,844</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>55,051</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>52.0%</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>115,153</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>131,970</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1,154</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>99,303</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>6,782</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>505</t>
         </is>
@@ -3731,70 +3973,75 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>jp_m19</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>▅M19A1</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#46</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>98,695</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>49,153</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>49.8%</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>111,879</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>56,948</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>26,875</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>86,121</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>2,201</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>199</t>
         </is>
@@ -3803,70 +4050,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>jp_type_1_chi_he</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Chi-He</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#47</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>96,586</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>51,371</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>53.2%</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>106,872</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>118,483</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>1,650</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>90,980</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>1,726</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>246</t>
         </is>
@@ -3875,70 +4127,75 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>jp_type_5_na_to</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Na-To</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.3#48</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>94,175</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>48,451</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>51.4%</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>101,420</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>106,772</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>225</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>84,779</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>2,799</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>236</t>
         </is>
@@ -3947,70 +4204,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>jp_type_81_tansam</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Type81(C)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.7#49</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>92,663</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>41,337</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>44.6%</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>114,963</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>59,272</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>76,453</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>3,209</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>243</t>
         </is>
@@ -4019,70 +4281,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>jp_type_98_ke_ni</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>Ke-Ni</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#50</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>91,342</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>42,448</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>46.5%</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>110,389</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>92,295</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>1,243</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>98,543</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>183</t>
         </is>
@@ -4091,70 +4358,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>jp_icv_prototype</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Type25RCV(P)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.7#51</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>82,348</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>41,643</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>50.6%</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>93,198</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>60,096</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>4,996</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>82,346</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>4,821</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>455</t>
         </is>
@@ -4163,70 +4435,75 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>jp_type_81_tansam_fcs</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Tan-SAMKai(TADS)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.0#52</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>81,525</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>39,943</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>49.0%</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>107,809</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>58,808</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>125,917</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>3,593</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>257</t>
         </is>
@@ -4235,70 +4512,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>jp_type_97_kai</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>Chi-HaKai</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#53</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>81,442</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>42,829</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>52.6%</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>90,240</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>91,867</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1,496</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>75,957</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>1,198</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>211</t>
         </is>
@@ -4307,70 +4589,75 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>jp_type_95_so_ki</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>So-Ki</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.0#54</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>77,287</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>37,697</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>48.8%</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>88,216</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>28,568</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>28,441</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>66,069</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>1,604</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>166</t>
         </is>
@@ -4379,70 +4666,75 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>jp_type_03_chusam_fcs</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>Type03(TADS)</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#55</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>74,388</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>37,978</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>51.1%</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>82,582</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>48,176</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>65,995</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>3,041</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>213</t>
         </is>
@@ -4451,70 +4743,75 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>jp_type_4_ho_ro</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>Ho-Ro</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#56</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>69,236</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>32,045</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>46.3%</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>76,974</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>48,925</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>1,155</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>66,893</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>122</t>
         </is>
@@ -4523,70 +4820,75 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>jp_halftrack_m16</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>▅M16MGMC</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#57</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>68,389</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>32,461</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>47.5%</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>78,523</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>12,485</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>33,004</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>58,332</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>1,048</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>148</t>
         </is>
@@ -4595,70 +4897,75 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>jp_type_3_ho_ni_I</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Ho-NiI</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.0#58</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>62,372</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>32,220</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>51.7%</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>68,453</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>72,745</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>59,118</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>1,242</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4667,70 +4974,75 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>jp_st_a2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>ST-A2</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#59</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>56,215</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>28,662</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>51.0%</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>60,647</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>58,969</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>172</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>51,841</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>5,258</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>336</t>
         </is>
@@ -4739,70 +5051,75 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>jp_type_2_ho_i</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>Ho-I</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Ранг 1БР 2.0#60</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>53,411</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>27,093</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>50.7%</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>59,546</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>64,089</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>917</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>50,544</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>965</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>198</t>
         </is>
@@ -4811,70 +5128,75 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>jp_type_97_chi_ha</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Chi-Ha</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#61</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>50,588</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>23,721</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>46.9%</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>55,166</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>39,524</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>1,393</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>46,901</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>367</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>145</t>
         </is>
@@ -4883,70 +5205,75 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>jp_type_98_ta_se</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>Ta-Se</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.7#62</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>50,327</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>25,207</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>50.1%</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>60,108</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>45,634</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>16,671</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>48,980</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>191</t>
         </is>
@@ -4955,70 +5282,75 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>jp_type_89b_i_go_otsu</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>I-GoKo</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#63</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>47,598</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>20,481</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>43.0%</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>55,016</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>26,138</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>47,200</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>106</t>
         </is>
@@ -5027,70 +5359,75 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>jp_type_3_ho_ni_III</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>Ho-NiIII</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#64</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>44,896</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>23,147</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>51.6%</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>48,722</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>50,711</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>40,025</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>1,611</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>198</t>
         </is>
@@ -5099,70 +5436,75 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>jp_type_94</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>Type94</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#65</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>42,508</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>20,084</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>47.2%</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>49,186</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>30,981</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>12,849</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>39,815</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>359</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>156</t>
         </is>
@@ -5171,70 +5513,75 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>jp_hiro_sha</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>Ro-GoExp.</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.7#66</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>41,600</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>20,270</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>48.7%</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>45,776</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>46,570</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>38,952</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>663</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>155</t>
         </is>
@@ -5243,70 +5590,75 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>jp_type_5_ho_ri_prototype</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>Ho-RiPrototype</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#67</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>33,824</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>18,343</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>54.2%</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>40,639</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>68,447</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>34,104</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>21,631</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>1,236</t>
         </is>
@@ -5315,70 +5667,75 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>jp_type_74_red_star</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>Type74RedStar</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.3#68</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>33,122</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>17,995</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>54.3%</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>43,548</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>47,030</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>38,940</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>17,913</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>1,235</t>
         </is>
@@ -5387,70 +5744,75 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>jp_type_2_ka_mi</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>Ka-Mi</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#69</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>27,109</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>12,619</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>46.5%</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>29,235</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>18,042</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>901</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>25,277</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>302</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>136</t>
         </is>
@@ -5459,70 +5821,75 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>jp_type_61_mod</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>Type61(B)</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#70</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>19,744</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>10,757</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>54.5%</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>26,025</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>31,890</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>23,424</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>18,955</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>1,202</t>
         </is>
@@ -5531,70 +5898,75 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>jp_type_60_atm</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>Type60ATM</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#71</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>18,592</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>9,391</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>50.5%</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>20,254</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>8,749</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>376</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>16,804</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>3,664</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>234</t>
         </is>
@@ -5603,70 +5975,75 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>jp_type_95_ha_go</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>Ha-Go</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#72</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>14,703</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>6,705</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>45.6%</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>15,852</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>8,271</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>13,845</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>0.53</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>293</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>132</t>
         </is>
@@ -5675,70 +6052,75 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>jp_pzkpfw_VI_ausf_e_tiger</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>▅HeavyTankNo.6</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#73</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>13,331</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>7,547</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>56.6%</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>15,931</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>28,581</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>13,852</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>20,517</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>1,186</t>
         </is>
@@ -5747,70 +6129,75 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>jp_type_3_ka_chi</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>Ka-Chi</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Ранг 1БР 2.0#74</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>13,113</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>7,765</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>59.2%</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>16,616</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>50,402</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>417</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>14,212</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>3.58</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>3,900</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>1,021</t>
         </is>
@@ -5819,70 +6206,75 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>jp_type_1_chi_he_5th_regiment</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>Chi-He(5thRegiment)</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#75</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>12,808</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>7,247</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>56.6%</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>15,832</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>20,169</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>13,702</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>5,212</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>714</t>
         </is>
@@ -5891,70 +6283,75 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>jp_type_75_mlrs</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>Type75MLRS</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.0#76</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>11,903</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>6,037</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>50.7%</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>14,268</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>12,402</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>244</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>12,662</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>13,944</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>938</t>
         </is>
@@ -5963,70 +6360,75 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>jp_type_97_chi_ha_12cm</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>Chi-HaShortGun</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Ранг 2БР 1.7#77</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>8,833</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>4,662</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>52.8%</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>10,307</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>13,436</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>8,757</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>3,459</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>523</t>
         </is>
@@ -6035,70 +6437,75 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>jp_type_95_ha_go_commander</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>Ha-GoCommander</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#78</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2,599</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>1,248</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>48.0%</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>3,036</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>1,841</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>2,714</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>272</t>
         </is>
@@ -6107,70 +6514,75 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>jp_type_95_heavy</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>Ro-Go</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#79</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>2,197</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>1,120</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>51.0%</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>2,620</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>2,807</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>2,290</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>2,644</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>502</t>
         </is>
@@ -6179,70 +6591,75 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>jp_type_97_kai_td</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>Chi-HaKaiTD</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#80</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>54.8%</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>2.75</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>2,231</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>547</t>
         </is>
@@ -6251,19 +6668,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>jp_type_81_tansam_launcher</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>Tan-SAMKai(TEL)</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.0#81</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6315,6 +6732,11 @@
         </is>
       </c>
       <c r="N82" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
